--- a/mode_docx_gen/pmi_mtz/part/lvrbvtr2/RVTR1.xlsx
+++ b/mode_docx_gen/pmi_mtz/part/lvrbvtr2/RVTR1.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23901"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\www_obj\mode_docx_gen\part\lvrbvtr2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\www5\mode_docx_gen\pmi_mtz\part\lvrbvtr2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68C41721-F5EE-4A6D-BB87-61B84BC5B54E}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="2325" windowWidth="15600" windowHeight="18720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="2325" windowWidth="15600" windowHeight="18720"/>
   </bookViews>
   <sheets>
     <sheet name="Signals" sheetId="1" r:id="rId1"/>
@@ -353,7 +352,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -761,7 +760,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AE14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2077,7 +2076,7 @@
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AD24">
+  <sortState ref="A2:AD24">
     <sortCondition ref="A1"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2086,7 +2085,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
